--- a/1376_Cuenca_Santa/_raw_reportes_xlsx/IDConfig_64998_completo.xlsx
+++ b/1376_Cuenca_Santa/_raw_reportes_xlsx/IDConfig_64998_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R82cf5872db9f4cdf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R8d8cc4561961476b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -174,7 +174,7 @@
       </x:c>
       <x:c s="" t="inlineStr">
         <x:is>
-          <x:t>Dpto: Ancash / Prov: Huaraz / Dist.: Huaraz</x:t>
+          <x:t>Dpto: Áncash / Prov: Huaraz / Dist.: Huaraz</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -250,6 +250,141 @@
         <x:is>
           <x:t>VALOR (m³/s)</x:t>
         </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.7547</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.4163</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.5027</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.5099</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3102</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.2556</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.6086</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.0981</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8482</x:v>
       </x:c>
     </x:row>
     <x:row>

--- a/1376_Cuenca_Santa/_raw_reportes_xlsx/IDConfig_64998_completo.xlsx
+++ b/1376_Cuenca_Santa/_raw_reportes_xlsx/IDConfig_64998_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R8d8cc4561961476b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R5480fcd479424e69"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0971</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.3751</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.3047</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.6753</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.6218</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.3047</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0330</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0303</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7702</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.4154</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6178</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7746</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.3485</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.2782</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.2699</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.2754</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.3230</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.4144</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.1318</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.5234</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.0958</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.4660</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.4575</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5607</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.6967</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8983</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.0538</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2948</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8769</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.0560</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.0561</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.6410</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.9584</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5759</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.3483</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.5187</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.1801</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.0087</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8469</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.1128</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.7538</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.6862</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.9562</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5160</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.1034</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5213</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
